--- a/outputs/model_output/2025-11-20/14-26-44_1/pivot.xlsx
+++ b/outputs/model_output/2025-11-20/14-26-44_1/pivot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crisp\Desktop\infrastructureinmotion\I-85\python model\outputs\model_output\2025-11-20\14-26-44_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E7D951-7742-4695-A124-E34115BB9E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412B3ADB-DFA9-42D0-9872-48689C966C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15416,7 +15416,7 @@
     <mergeCell ref="Z118:AF118"/>
   </mergeCells>
   <conditionalFormatting sqref="C23:P30">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15428,6 +15428,18 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S65:AF72">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9:P16">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
